--- a/01-进度计划/月度计划表/2026.09/土建/制浆车间施工进度计划表9月份.xlsx
+++ b/01-进度计划/月度计划表/2026.09/土建/制浆车间施工进度计划表9月份.xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mrseven\Desktop\总经办文档\01-进度计划\月度计划表\2026.09\土建\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowHeight="17775"/>
+    <workbookView windowWidth="23150" windowHeight="14080"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -875,7 +880,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -967,9 +972,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1276,7 +1278,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="7902575" y="3615055"/>
+          <a:off x="7910830" y="3672205"/>
           <a:ext cx="29210" cy="163830"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1313,7 +1315,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="7386955" y="1442720"/>
+          <a:off x="7395210" y="1461770"/>
           <a:ext cx="79375" cy="264795"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1350,7 +1352,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="7793990" y="3214370"/>
+          <a:off x="7802245" y="3271520"/>
           <a:ext cx="105410" cy="253365"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1387,7 +1389,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="7608570" y="4425950"/>
+          <a:off x="7616825" y="4483100"/>
           <a:ext cx="77470" cy="3175"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1424,7 +1426,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="7372350" y="1153160"/>
+          <a:off x="7380605" y="1172210"/>
           <a:ext cx="37465" cy="163830"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1461,7 +1463,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="7449820" y="2066290"/>
+          <a:off x="7458075" y="2085340"/>
           <a:ext cx="29210" cy="163195"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1498,7 +1500,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="7662545" y="2904490"/>
+          <a:off x="7670800" y="2923540"/>
           <a:ext cx="95885" cy="254000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1535,7 +1537,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="7536180" y="2529205"/>
+          <a:off x="7544435" y="2548255"/>
           <a:ext cx="95885" cy="254000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1791,7 +1793,7 @@
     <col min="1" max="1" width="5.375" style="1" customWidth="1"/>
     <col min="2" max="2" width="37.6833333333333" style="1" customWidth="1"/>
     <col min="3" max="3" width="7.875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="11.5" style="1" customWidth="1"/>
+    <col min="4" max="4" width="11.6083333333333" style="1" customWidth="1"/>
     <col min="5" max="5" width="10.75" style="1" customWidth="1"/>
     <col min="6" max="64" width="0.516666666666667" customWidth="1"/>
     <col min="65" max="66" width="0.45" customWidth="1"/>
@@ -1936,7 +1938,7 @@
       <c r="BL2" s="8"/>
       <c r="BM2" s="9"/>
     </row>
-    <row r="3" spans="1:121">
+    <row r="3" ht="15" spans="1:121">
       <c r="A3" s="5"/>
       <c r="B3" s="5"/>
       <c r="C3" s="5"/>
@@ -2067,7 +2069,7 @@
       <c r="DP3" s="11"/>
       <c r="DQ3" s="11"/>
     </row>
-    <row r="4" spans="1:121">
+    <row r="4" ht="15" spans="1:121">
       <c r="A4" s="5" t="s">
         <v>6</v>
       </c>
@@ -2877,7 +2879,7 @@
       <c r="BL13" s="15"/>
       <c r="BM13" s="16"/>
     </row>
-    <row r="14" ht="12" customHeight="1" spans="1:121">
+    <row r="14" ht="15" customHeight="1" spans="1:121">
       <c r="A14" s="10"/>
       <c r="B14" s="12"/>
       <c r="C14" s="10"/>
@@ -3441,11 +3443,11 @@
       <c r="BM21" s="30"/>
     </row>
     <row r="22" spans="1:65">
-      <c r="A22" s="31"/>
-      <c r="B22" s="31"/>
+      <c r="A22" s="24"/>
+      <c r="B22" s="24"/>
     </row>
     <row r="23" spans="1:65">
-      <c r="A23" s="31"/>
+      <c r="A23" s="24"/>
     </row>
   </sheetData>
   <mergeCells count="112">
